--- a/Class-6, Student Data-Main File-2026/s-D.xlsx
+++ b/Class-6, Student Data-Main File-2026/s-D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WLP Document\Student Data-Main File-2026\Class-6, Student Data-Main File-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68F370C-E925-4DA0-A387-9C19065B11F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE91836-BF0A-4D08-ADC4-98955CA5C056}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
